--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:38</t>
+    <t xml:space="preserve">2026-09-09 22:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:24</t>
+    <t xml:space="preserve">2026-09-12 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
@@ -36,88 +36,100 @@
     <t xml:space="preserve">Metropolitana</t>
   </si>
   <si>
+    <t xml:space="preserve">Santiago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providencia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Calera de Tango</t>
   </si>
   <si>
-    <t xml:space="preserve">Santiago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Providencia</t>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Miguel</t>
   </si>
   <si>
     <t xml:space="preserve">Pirque</t>
   </si>
   <si>
+    <t xml:space="preserve">Estación Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cisterna</t>
+  </si>
+  <si>
     <t xml:space="preserve">Independencia</t>
   </si>
   <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macul</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tiltil</t>
   </si>
   <si>
-    <t xml:space="preserve">Vitacura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ñuñoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estación Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Miguel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Cisterna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macul</t>
-  </si>
-  <si>
     <t xml:space="preserve">Quinta Normal</t>
   </si>
   <si>
     <t xml:space="preserve">La Reina</t>
   </si>
   <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lampa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padre Hurtado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alhué</t>
   </si>
   <si>
-    <t xml:space="preserve">Las Condes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerrillos</t>
+    <t xml:space="preserve">San Joaquín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ramón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
   </si>
   <si>
     <t xml:space="preserve">Lo Prado</t>
   </si>
   <si>
-    <t xml:space="preserve">San Joaquín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Ramón</t>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Granja</t>
   </si>
   <si>
     <t xml:space="preserve">Recoleta</t>
   </si>
   <si>
-    <t xml:space="preserve">Padre Hurtado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lampa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
     <t xml:space="preserve">El Bosque</t>
   </si>
   <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Florida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro</t>
+    <t xml:space="preserve">San José de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
   </si>
   <si>
     <t xml:space="preserve">Conchalí</t>
@@ -126,45 +138,36 @@
     <t xml:space="preserve">Lo Espejo</t>
   </si>
   <si>
-    <t xml:space="preserve">San José de Maipo</t>
+    <t xml:space="preserve">La Pintana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buin</t>
   </si>
   <si>
     <t xml:space="preserve">Pedro Aguirre Cerda</t>
   </si>
   <si>
-    <t xml:space="preserve">Huechuraba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pudahuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Pintana</t>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
   </si>
   <si>
     <t xml:space="preserve">María Pinto</t>
   </si>
   <si>
-    <t xml:space="preserve">Quilicura</t>
+    <t xml:space="preserve">Renca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paine</t>
   </si>
   <si>
     <t xml:space="preserve">San Bernardo</t>
   </si>
   <si>
-    <t xml:space="preserve">Colina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maipú</t>
   </si>
   <si>
@@ -177,18 +180,15 @@
     <t xml:space="preserve">Peñaflor</t>
   </si>
   <si>
-    <t xml:space="preserve">Paine</t>
+    <t xml:space="preserve">Curacaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Maipo</t>
   </si>
   <si>
     <t xml:space="preserve">El Monte</t>
   </si>
   <si>
-    <t xml:space="preserve">Isla de Maipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curacaví</t>
-  </si>
-  <si>
     <t xml:space="preserve">Melipilla</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:41</t>
+    <t xml:space="preserve">2026-09-24 00:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -631,13 +631,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>13403</v>
+        <v>13101</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>92.18</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="3">
@@ -648,13 +648,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>13101</v>
+        <v>13123</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>79.65</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="4">
@@ -665,13 +665,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>13123</v>
+        <v>13403</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>78.29</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="5">
@@ -682,13 +682,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>13202</v>
+        <v>13132</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>67.9</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="6">
@@ -699,13 +699,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>13108</v>
+        <v>13120</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>67.36</v>
+        <v>28.74</v>
       </c>
     </row>
     <row r="7">
@@ -716,13 +716,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>13303</v>
+        <v>13130</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>65.86</v>
+        <v>27.65</v>
       </c>
     </row>
     <row r="8">
@@ -733,13 +733,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>13132</v>
+        <v>13202</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>65.39</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="9">
@@ -750,13 +750,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>13120</v>
+        <v>13106</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>64.91</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="10">
@@ -767,13 +767,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>13106</v>
+        <v>13109</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>64.85</v>
+        <v>25.17</v>
       </c>
     </row>
     <row r="11">
@@ -784,13 +784,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>13130</v>
+        <v>13108</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>64.8</v>
+        <v>25.01</v>
       </c>
     </row>
     <row r="12">
@@ -801,13 +801,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>13109</v>
+        <v>13114</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>59.28</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="13">
@@ -824,7 +824,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>57.19</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="14">
@@ -835,13 +835,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>13126</v>
+        <v>13303</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>57.01</v>
+        <v>23.61</v>
       </c>
     </row>
     <row r="15">
@@ -852,13 +852,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>13113</v>
+        <v>13126</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>54.8</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="16">
@@ -869,13 +869,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>13502</v>
+        <v>13113</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>54.03</v>
+        <v>22.66</v>
       </c>
     </row>
     <row r="17">
@@ -886,13 +886,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>13114</v>
+        <v>13102</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>53.62</v>
+        <v>21.91</v>
       </c>
     </row>
     <row r="18">
@@ -903,13 +903,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>13102</v>
+        <v>13302</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>52.26</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="19">
@@ -920,13 +920,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>13117</v>
+        <v>13604</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>50.27</v>
+        <v>21.37</v>
       </c>
     </row>
     <row r="20">
@@ -937,13 +937,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>13129</v>
+        <v>13502</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>50.03</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="21">
@@ -954,13 +954,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>13131</v>
+        <v>13129</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>49.33</v>
+        <v>21.31</v>
       </c>
     </row>
     <row r="22">
@@ -971,13 +971,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>13127</v>
+        <v>13131</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>48.82</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="23">
@@ -988,13 +988,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>13604</v>
+        <v>13115</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>48.31</v>
+        <v>20.71</v>
       </c>
     </row>
     <row r="24">
@@ -1005,13 +1005,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>13302</v>
+        <v>13117</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>47.33</v>
+        <v>20.61</v>
       </c>
     </row>
     <row r="25">
@@ -1022,13 +1022,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>13111</v>
+        <v>13505</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>46.7</v>
+        <v>20.22</v>
       </c>
     </row>
     <row r="26">
@@ -1039,13 +1039,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>13105</v>
+        <v>13107</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>46.6</v>
+        <v>19.66</v>
       </c>
     </row>
     <row r="27">
@@ -1056,13 +1056,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>13115</v>
+        <v>13110</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>45.95</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="28">
@@ -1073,13 +1073,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>13110</v>
+        <v>13111</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>45.92</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="29">
@@ -1090,13 +1090,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>13505</v>
+        <v>13127</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>45.79</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="30">
@@ -1107,13 +1107,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>13104</v>
+        <v>13105</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>45.55</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="31">
@@ -1124,13 +1124,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>13116</v>
+        <v>13203</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>45.54</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="32">
@@ -1141,13 +1141,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>13203</v>
+        <v>13124</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>44.68</v>
+        <v>18.82</v>
       </c>
     </row>
     <row r="33">
@@ -1158,13 +1158,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>13121</v>
+        <v>13103</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>44.32</v>
+        <v>18.61</v>
       </c>
     </row>
     <row r="34">
@@ -1175,13 +1175,13 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>13107</v>
+        <v>13104</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>44.32</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="35">
@@ -1192,13 +1192,13 @@
         <v>39</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>13124</v>
+        <v>13116</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>44.06</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="36">
@@ -1209,13 +1209,13 @@
         <v>40</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>13103</v>
+        <v>13112</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>43.77</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="37">
@@ -1226,13 +1226,13 @@
         <v>41</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>13112</v>
+        <v>13402</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>41.87</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="38">
@@ -1243,13 +1243,13 @@
         <v>42</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>13504</v>
+        <v>13121</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>41.03</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="39">
@@ -1266,7 +1266,7 @@
         <v>2022</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>40.53</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="40">
@@ -1277,13 +1277,13 @@
         <v>44</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>13401</v>
+        <v>13301</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>39.39</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="41">
@@ -1294,13 +1294,13 @@
         <v>45</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>13301</v>
+        <v>13504</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>38.93</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="42">
@@ -1311,13 +1311,13 @@
         <v>46</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>13122</v>
+        <v>13128</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>38.49</v>
+        <v>16.39</v>
       </c>
     </row>
     <row r="43">
@@ -1328,13 +1328,13 @@
         <v>47</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13128</v>
+        <v>13122</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>38.05</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="44">
@@ -1345,13 +1345,13 @@
         <v>48</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>13402</v>
+        <v>13404</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>37.97</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="45">
@@ -1362,13 +1362,13 @@
         <v>49</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>13119</v>
+        <v>13401</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>37.92</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="46">
@@ -1379,13 +1379,13 @@
         <v>50</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>13601</v>
+        <v>13119</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>37.03</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="47">
@@ -1396,13 +1396,13 @@
         <v>51</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>13201</v>
+        <v>13601</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>36.23</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="48">
@@ -1413,13 +1413,13 @@
         <v>52</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>13605</v>
+        <v>13201</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>35.99</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="49">
@@ -1430,13 +1430,13 @@
         <v>53</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>13404</v>
+        <v>13605</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>35.17</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="50">
@@ -1447,13 +1447,13 @@
         <v>54</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>13602</v>
+        <v>13503</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>33.55</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="51">
@@ -1470,7 +1470,7 @@
         <v>2022</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>32.56</v>
+        <v>14.03</v>
       </c>
     </row>
     <row r="52">
@@ -1481,13 +1481,13 @@
         <v>56</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>13503</v>
+        <v>13602</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>32.25</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="53">
@@ -1504,7 +1504,7 @@
         <v>2022</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>24.82</v>
+        <v>10.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:18</t>
+    <t xml:space="preserve">2026-09-27 22:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:07</t>
+    <t xml:space="preserve">2026-09-29 11:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -637,7 +637,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>61.76</v>
+        <v>617.64</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34.9</v>
+        <v>348.96</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +671,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34.52</v>
+        <v>345.18</v>
       </c>
     </row>
     <row r="5">
@@ -688,7 +688,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>29.19</v>
+        <v>291.91</v>
       </c>
     </row>
     <row r="6">
@@ -705,7 +705,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28.74</v>
+        <v>287.44</v>
       </c>
     </row>
     <row r="7">
@@ -722,7 +722,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>27.65</v>
+        <v>276.51</v>
       </c>
     </row>
     <row r="8">
@@ -739,7 +739,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>26.88</v>
+        <v>268.81</v>
       </c>
     </row>
     <row r="9">
@@ -756,7 +756,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>25.29</v>
+        <v>252.86</v>
       </c>
     </row>
     <row r="10">
@@ -773,7 +773,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>25.17</v>
+        <v>251.68</v>
       </c>
     </row>
     <row r="11">
@@ -790,7 +790,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>25.01</v>
+        <v>250.14</v>
       </c>
     </row>
     <row r="12">
@@ -807,7 +807,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>24.7</v>
+        <v>246.97</v>
       </c>
     </row>
     <row r="13">
@@ -824,7 +824,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>24.32</v>
+        <v>243.18</v>
       </c>
     </row>
     <row r="14">
@@ -841,7 +841,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>23.61</v>
+        <v>236.14</v>
       </c>
     </row>
     <row r="15">
@@ -858,7 +858,7 @@
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>23.44</v>
+        <v>234.4</v>
       </c>
     </row>
     <row r="16">
@@ -875,7 +875,7 @@
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>22.66</v>
+        <v>226.57</v>
       </c>
     </row>
     <row r="17">
@@ -892,7 +892,7 @@
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>21.91</v>
+        <v>219.12</v>
       </c>
     </row>
     <row r="18">
@@ -909,7 +909,7 @@
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>21.44</v>
+        <v>214.43</v>
       </c>
     </row>
     <row r="19">
@@ -926,7 +926,7 @@
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>21.37</v>
+        <v>213.68</v>
       </c>
     </row>
     <row r="20">
@@ -943,7 +943,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>21.35</v>
+        <v>213.46</v>
       </c>
     </row>
     <row r="21">
@@ -960,7 +960,7 @@
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>21.31</v>
+        <v>213.14</v>
       </c>
     </row>
     <row r="22">
@@ -977,7 +977,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>20.93</v>
+        <v>209.31</v>
       </c>
     </row>
     <row r="23">
@@ -994,7 +994,7 @@
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>20.71</v>
+        <v>207.13</v>
       </c>
     </row>
     <row r="24">
@@ -1011,7 +1011,7 @@
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>20.61</v>
+        <v>206.12</v>
       </c>
     </row>
     <row r="25">
@@ -1028,7 +1028,7 @@
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>20.22</v>
+        <v>202.2</v>
       </c>
     </row>
     <row r="26">
@@ -1045,7 +1045,7 @@
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>19.66</v>
+        <v>196.6</v>
       </c>
     </row>
     <row r="27">
@@ -1062,7 +1062,7 @@
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>19.46</v>
+        <v>194.65</v>
       </c>
     </row>
     <row r="28">
@@ -1079,7 +1079,7 @@
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>19.28</v>
+        <v>192.84</v>
       </c>
     </row>
     <row r="29">
@@ -1096,7 +1096,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>19.16</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="30">
@@ -1113,7 +1113,7 @@
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>19.07</v>
+        <v>190.66</v>
       </c>
     </row>
     <row r="31">
@@ -1130,7 +1130,7 @@
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>18.97</v>
+        <v>189.74</v>
       </c>
     </row>
     <row r="32">
@@ -1147,7 +1147,7 @@
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18.82</v>
+        <v>188.22</v>
       </c>
     </row>
     <row r="33">
@@ -1164,7 +1164,7 @@
         <v>2022</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>18.61</v>
+        <v>186.07</v>
       </c>
     </row>
     <row r="34">
@@ -1181,7 +1181,7 @@
         <v>2022</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>18.44</v>
+        <v>184.36</v>
       </c>
     </row>
     <row r="35">
@@ -1198,7 +1198,7 @@
         <v>2022</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>18.4</v>
+        <v>183.96</v>
       </c>
     </row>
     <row r="36">
@@ -1215,7 +1215,7 @@
         <v>2022</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>17.71</v>
+        <v>177.07</v>
       </c>
     </row>
     <row r="37">
@@ -1232,7 +1232,7 @@
         <v>2022</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>17.47</v>
+        <v>174.66</v>
       </c>
     </row>
     <row r="38">
@@ -1249,7 +1249,7 @@
         <v>2022</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>17.37</v>
+        <v>173.67</v>
       </c>
     </row>
     <row r="39">
@@ -1266,7 +1266,7 @@
         <v>2022</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>17.33</v>
+        <v>173.34</v>
       </c>
     </row>
     <row r="40">
@@ -1283,7 +1283,7 @@
         <v>2022</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>16.81</v>
+        <v>168.07</v>
       </c>
     </row>
     <row r="41">
@@ -1300,7 +1300,7 @@
         <v>2022</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>16.57</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="42">
@@ -1317,7 +1317,7 @@
         <v>2022</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>16.39</v>
+        <v>163.93</v>
       </c>
     </row>
     <row r="43">
@@ -1334,7 +1334,7 @@
         <v>2022</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>16.38</v>
+        <v>163.78</v>
       </c>
     </row>
     <row r="44">
@@ -1351,7 +1351,7 @@
         <v>2022</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>16.33</v>
+        <v>163.26</v>
       </c>
     </row>
     <row r="45">
@@ -1368,7 +1368,7 @@
         <v>2022</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>16.28</v>
+        <v>162.76</v>
       </c>
     </row>
     <row r="46">
@@ -1385,7 +1385,7 @@
         <v>2022</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>16.1</v>
+        <v>161.02</v>
       </c>
     </row>
     <row r="47">
@@ -1402,7 +1402,7 @@
         <v>2022</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>15.4</v>
+        <v>153.98</v>
       </c>
     </row>
     <row r="48">
@@ -1419,7 +1419,7 @@
         <v>2022</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>15.36</v>
+        <v>153.61</v>
       </c>
     </row>
     <row r="49">
@@ -1436,7 +1436,7 @@
         <v>2022</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>15.15</v>
+        <v>151.49</v>
       </c>
     </row>
     <row r="50">
@@ -1453,7 +1453,7 @@
         <v>2022</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>15.03</v>
+        <v>150.35</v>
       </c>
     </row>
     <row r="51">
@@ -1470,7 +1470,7 @@
         <v>2022</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>14.03</v>
+        <v>140.29</v>
       </c>
     </row>
     <row r="52">
@@ -1487,7 +1487,7 @@
         <v>2022</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>13.54</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="53">
@@ -1504,7 +1504,7 @@
         <v>2022</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>10.5</v>
+        <v>105.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:02</t>
+    <t xml:space="preserve">2026-10-01 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -219,7 +219,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:27</t>
+    <t xml:space="preserve">2026-10-02 13:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:15</t>
+    <t xml:space="preserve">2026-10-05 07:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
